--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2B59D18754AA30699B5B241159ADF8F172DDE611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF064B69-9A85-4BA3-AAAF-EB2F98811D1C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D18754AA30699B5B241159ADF8F172DDE611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB11D27-1366-4997-B417-D48D41699618}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,6 +573,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-10.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,19 +911,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S9" t="n">
